--- a/Data Dummy Pendaftaran Peserta Baru (Perorangan).xlsx
+++ b/Data Dummy Pendaftaran Peserta Baru (Perorangan).xlsx
@@ -299,7 +299,7 @@
       </c>
       <c r="M2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">142376</t>
+          <t xml:space="preserve">271048</t>
         </is>
       </c>
       <c r="N2" t="inlineStr" s="0">
@@ -486,7 +486,7 @@
       </c>
       <c r="M3" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">163890</t>
+          <t xml:space="preserve">283615</t>
         </is>
       </c>
       <c r="N3" t="inlineStr" s="0">
